--- a/output/laminas_comunales/comunal_i_peringr_median_a_2023_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2023_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F8"/>
+  <dimension ref="A1:E8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -381,11 +381,6 @@
           <t>delta_pct</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>is_emph</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -405,9 +400,6 @@
       <c r="E2">
         <v>-6.333567909922588</v>
       </c>
-      <c r="F2" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -427,9 +419,6 @@
       <c r="E3">
         <v>-7.974980453479274</v>
       </c>
-      <c r="F3" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -449,9 +438,6 @@
       <c r="E4">
         <v>17.9671457905544</v>
       </c>
-      <c r="F4" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -471,9 +457,6 @@
       <c r="E5">
         <v>-7.185628742514972</v>
       </c>
-      <c r="F5" t="b">
-        <v>0</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -493,9 +476,6 @@
       <c r="E6">
         <v>-4.228329809725162</v>
       </c>
-      <c r="F6" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -515,9 +495,6 @@
       <c r="E7">
         <v>3.74707259953162</v>
       </c>
-      <c r="F7" t="b">
-        <v>1</v>
-      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -536,9 +513,6 @@
       </c>
       <c r="E8">
         <v>-6.392694063926951</v>
-      </c>
-      <c r="F8" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>

--- a/output/laminas_comunales/comunal_i_peringr_median_a_2023_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2023_tarapaca.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E8"/>
+  <dimension ref="A1:E9"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -461,57 +461,76 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Iquique</t>
+          <t>Promedio Regional</t>
         </is>
       </c>
       <c r="B6">
-        <v>9.06</v>
+        <v>9.67</v>
       </c>
       <c r="C6">
-        <v>9.460000000000001</v>
+        <v>10.15</v>
       </c>
       <c r="D6">
-        <v>-0.4000000000000004</v>
+        <v>-0.4800000000000004</v>
       </c>
       <c r="E6">
-        <v>-4.228329809725162</v>
+        <v>-4.72906403940887</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
+          <t>Iquique</t>
         </is>
       </c>
       <c r="B7">
-        <v>8.859999999999999</v>
+        <v>9.06</v>
       </c>
       <c r="C7">
-        <v>8.539999999999999</v>
+        <v>9.460000000000001</v>
       </c>
       <c r="D7">
-        <v>0.3200000000000003</v>
+        <v>-0.4000000000000004</v>
       </c>
       <c r="E7">
-        <v>3.74707259953162</v>
+        <v>-4.228329809725162</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
+          <t>Pozo Almonte</t>
+        </is>
+      </c>
+      <c r="B8">
+        <v>8.859999999999999</v>
+      </c>
+      <c r="C8">
+        <v>8.539999999999999</v>
+      </c>
+      <c r="D8">
+        <v>0.3200000000000003</v>
+      </c>
+      <c r="E8">
+        <v>3.74707259953162</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
           <t>Pica</t>
         </is>
       </c>
-      <c r="B8">
+      <c r="B9">
         <v>8.199999999999999</v>
       </c>
-      <c r="C8">
+      <c r="C9">
         <v>8.76</v>
       </c>
-      <c r="D8">
+      <c r="D9">
         <v>-0.5600000000000005</v>
       </c>
-      <c r="E8">
+      <c r="E9">
         <v>-6.392694063926951</v>
       </c>
     </row>

--- a/output/laminas_comunales/comunal_i_peringr_median_a_2023_tarapaca.xlsx
+++ b/output/laminas_comunales/comunal_i_peringr_median_a_2023_tarapaca.xlsx
@@ -541,7 +541,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -550,40 +550,26 @@
           <t>Comuna</t>
         </is>
       </c>
-      <c r="B1" s="1" t="inlineStr">
-        <is>
-          <t>2023</t>
-        </is>
-      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Alto Hospicio</t>
-        </is>
-      </c>
-      <c r="B2">
-        <v>10.85</v>
+          <t>Camiña</t>
+        </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Camiña</t>
-        </is>
-      </c>
-      <c r="B3">
-        <v>11.49</v>
+          <t>Colchane</t>
+        </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Colchane</t>
-        </is>
-      </c>
-      <c r="B4">
-        <v>13.31</v>
+          <t>Pozo Almonte</t>
+        </is>
       </c>
     </row>
     <row r="5">
@@ -592,38 +578,26 @@
           <t>Huara</t>
         </is>
       </c>
-      <c r="B5">
-        <v>11.77</v>
-      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Iquique</t>
-        </is>
-      </c>
-      <c r="B6">
-        <v>9.06</v>
+          <t>Alto Hospicio</t>
+        </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Pica</t>
-        </is>
-      </c>
-      <c r="B7">
-        <v>8.199999999999999</v>
+          <t>Iquique</t>
+        </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Pozo Almonte</t>
-        </is>
-      </c>
-      <c r="B8">
-        <v>8.859999999999999</v>
+          <t>Pica</t>
+        </is>
       </c>
     </row>
   </sheetData>
